--- a/certificates.xlsx
+++ b/certificates.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pat\Desktop\Python Pro\Academy_Certificates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahmed\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="355">
   <si>
     <t>اسم المعلم</t>
   </si>
@@ -1096,7 +1096,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="178"/>
       <scheme val="minor"/>
@@ -1116,7 +1116,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1157,7 +1157,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1175,7 +1175,6 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1488,18 +1487,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G345"/>
-  <sheetFormatPr defaultRowHeight="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
-    <col min="4" max="4" width="23.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="29.28515625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="9" customWidth="1"/>
-    <col min="7" max="7" width="19.28515625" customWidth="1"/>
+    <col min="3" max="3" width="20.875" customWidth="1"/>
+    <col min="4" max="4" width="23.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="29.25" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16.125" style="8" customWidth="1"/>
+    <col min="7" max="7" width="19.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>354</v>
       </c>
@@ -1538,10 +1537,12 @@
       <c r="E2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="7">
         <v>45169</v>
       </c>
-      <c r="G2" s="7"/>
+      <c r="G2" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="3" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
@@ -1559,10 +1560,12 @@
       <c r="E3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="7">
         <v>45169</v>
       </c>
-      <c r="G3" s="7"/>
+      <c r="G3" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="4" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
@@ -1580,10 +1583,12 @@
       <c r="E4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="7">
         <v>45169</v>
       </c>
-      <c r="G4" s="7"/>
+      <c r="G4" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="5" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
@@ -1601,10 +1606,12 @@
       <c r="E5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="7">
         <v>45169</v>
       </c>
-      <c r="G5" s="7"/>
+      <c r="G5" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="6" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
@@ -1622,10 +1629,12 @@
       <c r="E6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="7">
         <v>45169</v>
       </c>
-      <c r="G6" s="7"/>
+      <c r="G6" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="7" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
@@ -1643,10 +1652,12 @@
       <c r="E7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="7">
         <v>45169</v>
       </c>
-      <c r="G7" s="7"/>
+      <c r="G7" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
@@ -1664,10 +1675,12 @@
       <c r="E8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="7">
         <v>45169</v>
       </c>
-      <c r="G8" s="7"/>
+      <c r="G8" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="9" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
@@ -1685,11 +1698,11 @@
       <c r="E9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="7">
         <v>45169</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1708,11 +1721,11 @@
       <c r="E10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="7">
         <v>45169</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1731,7 +1744,7 @@
       <c r="E11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="7">
         <v>45169</v>
       </c>
       <c r="G11" s="2" t="s">
@@ -1754,10 +1767,12 @@
       <c r="E12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="7">
         <v>45169</v>
       </c>
-      <c r="G12" s="7"/>
+      <c r="G12" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="13" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
@@ -1775,10 +1790,12 @@
       <c r="E13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="7">
         <v>45169</v>
       </c>
-      <c r="G13" s="7"/>
+      <c r="G13" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="14" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
@@ -1796,10 +1813,12 @@
       <c r="E14" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="7">
         <v>45200</v>
       </c>
-      <c r="G14" s="7"/>
+      <c r="G14" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="15" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
@@ -1817,10 +1836,12 @@
       <c r="E15" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="7">
         <v>45200</v>
       </c>
-      <c r="G15" s="7"/>
+      <c r="G15" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="16" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
@@ -1838,10 +1859,12 @@
       <c r="E16" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="7">
         <v>45200</v>
       </c>
-      <c r="G16" s="7"/>
+      <c r="G16" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="17" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
@@ -1859,10 +1882,12 @@
       <c r="E17" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="7">
         <v>45200</v>
       </c>
-      <c r="G17" s="7"/>
+      <c r="G17" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="18" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
@@ -1880,7 +1905,7 @@
       <c r="E18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="7">
         <v>45200</v>
       </c>
       <c r="G18" s="2" t="s">
@@ -1903,7 +1928,7 @@
       <c r="E19" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="7">
         <v>45200</v>
       </c>
       <c r="G19" s="2" t="s">
@@ -1926,7 +1951,7 @@
       <c r="E20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="7">
         <v>45200</v>
       </c>
       <c r="G20" s="2" t="s">
@@ -1949,11 +1974,11 @@
       <c r="E21" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="7">
         <v>45200</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1972,7 +1997,7 @@
       <c r="E22" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="7">
         <v>45200</v>
       </c>
       <c r="G22" s="2" t="s">
@@ -1995,7 +2020,7 @@
       <c r="E23" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="7">
         <v>45200</v>
       </c>
       <c r="G23" s="2" t="s">
@@ -2018,7 +2043,7 @@
       <c r="E24" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="7">
         <v>45200</v>
       </c>
       <c r="G24" s="2" t="s">
@@ -2041,7 +2066,7 @@
       <c r="E25" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="7">
         <v>45211</v>
       </c>
       <c r="G25" s="2" t="s">
@@ -2064,7 +2089,7 @@
       <c r="E26" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="7">
         <v>45211</v>
       </c>
       <c r="G26" s="2" t="s">
@@ -2087,7 +2112,7 @@
       <c r="E27" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="7">
         <v>45211</v>
       </c>
       <c r="G27" s="2" t="s">
@@ -2110,7 +2135,7 @@
       <c r="E28" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="7">
         <v>45211</v>
       </c>
       <c r="G28" s="2" t="s">
@@ -2133,7 +2158,7 @@
       <c r="E29" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="7">
         <v>45211</v>
       </c>
       <c r="G29" s="2" t="s">
@@ -2156,10 +2181,12 @@
       <c r="E30" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="7">
         <v>45211</v>
       </c>
-      <c r="G30" s="7"/>
+      <c r="G30" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="31" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
@@ -2177,10 +2204,12 @@
       <c r="E31" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F31" s="8">
+      <c r="F31" s="7">
         <v>45211</v>
       </c>
-      <c r="G31" s="7"/>
+      <c r="G31" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="32" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
@@ -2198,10 +2227,12 @@
       <c r="E32" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F32" s="8">
+      <c r="F32" s="7">
         <v>45211</v>
       </c>
-      <c r="G32" s="7"/>
+      <c r="G32" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="33" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
@@ -2219,10 +2250,12 @@
       <c r="E33" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F33" s="8">
+      <c r="F33" s="7">
         <v>45211</v>
       </c>
-      <c r="G33" s="7"/>
+      <c r="G33" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="34" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
@@ -2240,10 +2273,12 @@
       <c r="E34" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F34" s="8">
+      <c r="F34" s="7">
         <v>45211</v>
       </c>
-      <c r="G34" s="7"/>
+      <c r="G34" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="35" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
@@ -2261,10 +2296,12 @@
       <c r="E35" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F35" s="8">
+      <c r="F35" s="7">
         <v>45211</v>
       </c>
-      <c r="G35" s="7"/>
+      <c r="G35" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="36" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
@@ -2282,10 +2319,12 @@
       <c r="E36" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F36" s="8">
+      <c r="F36" s="7">
         <v>45211</v>
       </c>
-      <c r="G36" s="7"/>
+      <c r="G36" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="37" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
@@ -2303,10 +2342,12 @@
       <c r="E37" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F37" s="8">
+      <c r="F37" s="7">
         <v>45211</v>
       </c>
-      <c r="G37" s="7"/>
+      <c r="G37" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="38" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
@@ -2324,10 +2365,12 @@
       <c r="E38" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F38" s="8">
+      <c r="F38" s="7">
         <v>45211</v>
       </c>
-      <c r="G38" s="7"/>
+      <c r="G38" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="39" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
@@ -2345,10 +2388,12 @@
       <c r="E39" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F39" s="8">
+      <c r="F39" s="7">
         <v>45211</v>
       </c>
-      <c r="G39" s="7"/>
+      <c r="G39" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="40" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
@@ -2366,10 +2411,12 @@
       <c r="E40" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F40" s="8">
+      <c r="F40" s="7">
         <v>45260</v>
       </c>
-      <c r="G40" s="7"/>
+      <c r="G40" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="41" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
@@ -2387,10 +2434,12 @@
       <c r="E41" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F41" s="8">
+      <c r="F41" s="7">
         <v>45260</v>
       </c>
-      <c r="G41" s="7"/>
+      <c r="G41" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="42" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
@@ -2408,10 +2457,12 @@
       <c r="E42" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F42" s="8">
+      <c r="F42" s="7">
         <v>45260</v>
       </c>
-      <c r="G42" s="7"/>
+      <c r="G42" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="43" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
@@ -2429,10 +2480,12 @@
       <c r="E43" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="8">
+      <c r="F43" s="7">
         <v>45260</v>
       </c>
-      <c r="G43" s="7"/>
+      <c r="G43" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="44" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
@@ -2450,10 +2503,12 @@
       <c r="E44" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F44" s="8">
+      <c r="F44" s="7">
         <v>45260</v>
       </c>
-      <c r="G44" s="7"/>
+      <c r="G44" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="45" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
@@ -2471,10 +2526,12 @@
       <c r="E45" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F45" s="8">
+      <c r="F45" s="7">
         <v>45260</v>
       </c>
-      <c r="G45" s="7"/>
+      <c r="G45" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="46" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
@@ -2492,7 +2549,7 @@
       <c r="E46" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F46" s="8">
+      <c r="F46" s="7">
         <v>45260</v>
       </c>
       <c r="G46" s="2" t="s">
@@ -2515,7 +2572,7 @@
       <c r="E47" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F47" s="8">
+      <c r="F47" s="7">
         <v>45260</v>
       </c>
       <c r="G47" s="2" t="s">
@@ -2538,7 +2595,7 @@
       <c r="E48" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F48" s="8">
+      <c r="F48" s="7">
         <v>45260</v>
       </c>
       <c r="G48" s="2" t="s">
@@ -2561,11 +2618,11 @@
       <c r="E49" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F49" s="8">
+      <c r="F49" s="7">
         <v>45260</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2584,7 +2641,7 @@
       <c r="E50" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F50" s="8">
+      <c r="F50" s="7">
         <v>45260</v>
       </c>
       <c r="G50" s="2" t="s">
@@ -2607,7 +2664,7 @@
       <c r="E51" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F51" s="8">
+      <c r="F51" s="7">
         <v>45260</v>
       </c>
       <c r="G51" s="2" t="s">
@@ -2630,7 +2687,7 @@
       <c r="E52" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F52" s="8">
+      <c r="F52" s="7">
         <v>45260</v>
       </c>
       <c r="G52" s="2" t="s">
@@ -2653,7 +2710,7 @@
       <c r="E53" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F53" s="8">
+      <c r="F53" s="7">
         <v>45260</v>
       </c>
       <c r="G53" s="2" t="s">
@@ -2676,7 +2733,7 @@
       <c r="E54" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F54" s="8">
+      <c r="F54" s="7">
         <v>45260</v>
       </c>
       <c r="G54" s="2" t="s">
@@ -2699,10 +2756,12 @@
       <c r="E55" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F55" s="8">
+      <c r="F55" s="7">
         <v>45260</v>
       </c>
-      <c r="G55" s="7"/>
+      <c r="G55" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="56" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
@@ -2720,10 +2779,12 @@
       <c r="E56" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F56" s="8">
+      <c r="F56" s="7">
         <v>45287</v>
       </c>
-      <c r="G56" s="7"/>
+      <c r="G56" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="57" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
@@ -2741,10 +2802,12 @@
       <c r="E57" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F57" s="8">
+      <c r="F57" s="7">
         <v>45287</v>
       </c>
-      <c r="G57" s="7"/>
+      <c r="G57" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="58" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
@@ -2762,10 +2825,12 @@
       <c r="E58" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F58" s="8">
+      <c r="F58" s="7">
         <v>45287</v>
       </c>
-      <c r="G58" s="7"/>
+      <c r="G58" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="59" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
@@ -2783,10 +2848,12 @@
       <c r="E59" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F59" s="8">
+      <c r="F59" s="7">
         <v>45287</v>
       </c>
-      <c r="G59" s="7"/>
+      <c r="G59" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="60" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
@@ -2804,10 +2871,12 @@
       <c r="E60" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F60" s="8">
+      <c r="F60" s="7">
         <v>45287</v>
       </c>
-      <c r="G60" s="7"/>
+      <c r="G60" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="61" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
@@ -2825,10 +2894,12 @@
       <c r="E61" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F61" s="8">
+      <c r="F61" s="7">
         <v>45287</v>
       </c>
-      <c r="G61" s="7"/>
+      <c r="G61" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="62" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
@@ -2846,10 +2917,12 @@
       <c r="E62" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F62" s="8">
+      <c r="F62" s="7">
         <v>45287</v>
       </c>
-      <c r="G62" s="7"/>
+      <c r="G62" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="63" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
@@ -2867,10 +2940,12 @@
       <c r="E63" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F63" s="8">
+      <c r="F63" s="7">
         <v>45287</v>
       </c>
-      <c r="G63" s="7"/>
+      <c r="G63" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="64" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
@@ -2888,10 +2963,12 @@
       <c r="E64" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F64" s="8">
+      <c r="F64" s="7">
         <v>45287</v>
       </c>
-      <c r="G64" s="7"/>
+      <c r="G64" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="65" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
@@ -2909,10 +2986,12 @@
       <c r="E65" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F65" s="8">
+      <c r="F65" s="7">
         <v>45287</v>
       </c>
-      <c r="G65" s="7"/>
+      <c r="G65" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="66" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
@@ -2930,10 +3009,12 @@
       <c r="E66" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F66" s="8">
+      <c r="F66" s="7">
         <v>45287</v>
       </c>
-      <c r="G66" s="7"/>
+      <c r="G66" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="67" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
@@ -2951,10 +3032,12 @@
       <c r="E67" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F67" s="8">
+      <c r="F67" s="7">
         <v>45287</v>
       </c>
-      <c r="G67" s="7"/>
+      <c r="G67" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="68" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
@@ -2972,10 +3055,12 @@
       <c r="E68" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F68" s="8">
+      <c r="F68" s="7">
         <v>45287</v>
       </c>
-      <c r="G68" s="7"/>
+      <c r="G68" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="69" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
@@ -2993,10 +3078,12 @@
       <c r="E69" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F69" s="8">
+      <c r="F69" s="7">
         <v>45287</v>
       </c>
-      <c r="G69" s="7"/>
+      <c r="G69" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="70" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
@@ -3014,10 +3101,12 @@
       <c r="E70" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F70" s="8">
+      <c r="F70" s="7">
         <v>45287</v>
       </c>
-      <c r="G70" s="7"/>
+      <c r="G70" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="71" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
@@ -3035,10 +3124,12 @@
       <c r="E71" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F71" s="8">
+      <c r="F71" s="7">
         <v>45287</v>
       </c>
-      <c r="G71" s="7"/>
+      <c r="G71" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="72" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
@@ -3056,10 +3147,12 @@
       <c r="E72" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F72" s="8">
+      <c r="F72" s="7">
         <v>45287</v>
       </c>
-      <c r="G72" s="7"/>
+      <c r="G72" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="73" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
@@ -3077,10 +3170,12 @@
       <c r="E73" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F73" s="8">
+      <c r="F73" s="7">
         <v>45287</v>
       </c>
-      <c r="G73" s="7"/>
+      <c r="G73" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="74" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
@@ -3098,10 +3193,12 @@
       <c r="E74" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F74" s="8">
+      <c r="F74" s="7">
         <v>45287</v>
       </c>
-      <c r="G74" s="7"/>
+      <c r="G74" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="75" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
@@ -3119,10 +3216,12 @@
       <c r="E75" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F75" s="8">
+      <c r="F75" s="7">
         <v>45287</v>
       </c>
-      <c r="G75" s="7"/>
+      <c r="G75" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="76" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
@@ -3140,10 +3239,12 @@
       <c r="E76" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F76" s="8">
+      <c r="F76" s="7">
         <v>45323</v>
       </c>
-      <c r="G76" s="7"/>
+      <c r="G76" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="77" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
@@ -3161,10 +3262,12 @@
       <c r="E77" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F77" s="8">
+      <c r="F77" s="7">
         <v>45323</v>
       </c>
-      <c r="G77" s="7"/>
+      <c r="G77" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="78" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
@@ -3182,10 +3285,12 @@
       <c r="E78" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F78" s="8">
+      <c r="F78" s="7">
         <v>45323</v>
       </c>
-      <c r="G78" s="7"/>
+      <c r="G78" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="79" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
@@ -3203,10 +3308,12 @@
       <c r="E79" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F79" s="8">
+      <c r="F79" s="7">
         <v>45323</v>
       </c>
-      <c r="G79" s="7"/>
+      <c r="G79" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="80" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
@@ -3224,10 +3331,12 @@
       <c r="E80" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F80" s="8">
+      <c r="F80" s="7">
         <v>45323</v>
       </c>
-      <c r="G80" s="7"/>
+      <c r="G80" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="81" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
@@ -3245,10 +3354,12 @@
       <c r="E81" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F81" s="8">
+      <c r="F81" s="7">
         <v>45323</v>
       </c>
-      <c r="G81" s="7"/>
+      <c r="G81" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="82" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
@@ -3266,10 +3377,12 @@
       <c r="E82" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F82" s="8">
+      <c r="F82" s="7">
         <v>45323</v>
       </c>
-      <c r="G82" s="7"/>
+      <c r="G82" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="83" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
@@ -3287,10 +3400,12 @@
       <c r="E83" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F83" s="8">
+      <c r="F83" s="7">
         <v>45323</v>
       </c>
-      <c r="G83" s="7"/>
+      <c r="G83" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="84" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
@@ -3308,10 +3423,12 @@
       <c r="E84" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F84" s="8">
+      <c r="F84" s="7">
         <v>45323</v>
       </c>
-      <c r="G84" s="7"/>
+      <c r="G84" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="85" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
@@ -3329,10 +3446,12 @@
       <c r="E85" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F85" s="8">
+      <c r="F85" s="7">
         <v>45323</v>
       </c>
-      <c r="G85" s="7"/>
+      <c r="G85" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="86" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
@@ -3350,10 +3469,12 @@
       <c r="E86" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F86" s="8">
+      <c r="F86" s="7">
         <v>45323</v>
       </c>
-      <c r="G86" s="7"/>
+      <c r="G86" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="87" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
@@ -3371,10 +3492,12 @@
       <c r="E87" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F87" s="8">
+      <c r="F87" s="7">
         <v>45323</v>
       </c>
-      <c r="G87" s="7"/>
+      <c r="G87" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="88" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
@@ -3392,10 +3515,12 @@
       <c r="E88" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F88" s="8">
+      <c r="F88" s="7">
         <v>45323</v>
       </c>
-      <c r="G88" s="7"/>
+      <c r="G88" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="89" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
@@ -3413,10 +3538,12 @@
       <c r="E89" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F89" s="8">
+      <c r="F89" s="7">
         <v>45323</v>
       </c>
-      <c r="G89" s="7"/>
+      <c r="G89" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="90" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
@@ -3434,10 +3561,12 @@
       <c r="E90" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F90" s="8">
+      <c r="F90" s="7">
         <v>45323</v>
       </c>
-      <c r="G90" s="7"/>
+      <c r="G90" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="91" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
@@ -3455,10 +3584,12 @@
       <c r="E91" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F91" s="8">
+      <c r="F91" s="7">
         <v>45323</v>
       </c>
-      <c r="G91" s="7"/>
+      <c r="G91" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="92" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
@@ -3476,10 +3607,12 @@
       <c r="E92" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F92" s="8">
+      <c r="F92" s="7">
         <v>45323</v>
       </c>
-      <c r="G92" s="7"/>
+      <c r="G92" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="93" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
@@ -3497,10 +3630,12 @@
       <c r="E93" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F93" s="8">
+      <c r="F93" s="7">
         <v>45323</v>
       </c>
-      <c r="G93" s="7"/>
+      <c r="G93" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="94" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
@@ -3518,10 +3653,12 @@
       <c r="E94" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F94" s="8">
+      <c r="F94" s="7">
         <v>45323</v>
       </c>
-      <c r="G94" s="7"/>
+      <c r="G94" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="95" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
@@ -3539,10 +3676,12 @@
       <c r="E95" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F95" s="8">
+      <c r="F95" s="7">
         <v>45323</v>
       </c>
-      <c r="G95" s="7"/>
+      <c r="G95" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="96" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
@@ -3560,10 +3699,12 @@
       <c r="E96" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F96" s="8">
+      <c r="F96" s="7">
         <v>45323</v>
       </c>
-      <c r="G96" s="7"/>
+      <c r="G96" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="97" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
@@ -3581,10 +3722,12 @@
       <c r="E97" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F97" s="8">
+      <c r="F97" s="7">
         <v>45323</v>
       </c>
-      <c r="G97" s="7"/>
+      <c r="G97" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="98" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
@@ -3602,10 +3745,12 @@
       <c r="E98" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F98" s="8">
+      <c r="F98" s="7">
         <v>45323</v>
       </c>
-      <c r="G98" s="7"/>
+      <c r="G98" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="99" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
@@ -3623,10 +3768,12 @@
       <c r="E99" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F99" s="8">
+      <c r="F99" s="7">
         <v>45323</v>
       </c>
-      <c r="G99" s="7"/>
+      <c r="G99" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="100" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
@@ -3644,10 +3791,12 @@
       <c r="E100" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F100" s="8">
+      <c r="F100" s="7">
         <v>45323</v>
       </c>
-      <c r="G100" s="7"/>
+      <c r="G100" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="101" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
@@ -3665,10 +3814,12 @@
       <c r="E101" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F101" s="8">
+      <c r="F101" s="7">
         <v>45323</v>
       </c>
-      <c r="G101" s="7"/>
+      <c r="G101" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="102" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="4">
@@ -3686,10 +3837,12 @@
       <c r="E102" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F102" s="8">
+      <c r="F102" s="7">
         <v>45323</v>
       </c>
-      <c r="G102" s="7"/>
+      <c r="G102" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="103" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
@@ -3707,10 +3860,12 @@
       <c r="E103" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F103" s="8">
+      <c r="F103" s="7">
         <v>45385</v>
       </c>
-      <c r="G103" s="7"/>
+      <c r="G103" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="104" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="4">
@@ -3728,10 +3883,12 @@
       <c r="E104" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F104" s="8">
+      <c r="F104" s="7">
         <v>45385</v>
       </c>
-      <c r="G104" s="7"/>
+      <c r="G104" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="105" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="4">
@@ -3749,10 +3906,12 @@
       <c r="E105" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F105" s="8">
+      <c r="F105" s="7">
         <v>45385</v>
       </c>
-      <c r="G105" s="7"/>
+      <c r="G105" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="106" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="4">
@@ -3770,10 +3929,12 @@
       <c r="E106" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F106" s="8">
+      <c r="F106" s="7">
         <v>45385</v>
       </c>
-      <c r="G106" s="7"/>
+      <c r="G106" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="107" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
@@ -3791,10 +3952,12 @@
       <c r="E107" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F107" s="8">
+      <c r="F107" s="7">
         <v>45385</v>
       </c>
-      <c r="G107" s="7"/>
+      <c r="G107" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="108" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="4">
@@ -3812,10 +3975,12 @@
       <c r="E108" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F108" s="8">
+      <c r="F108" s="7">
         <v>45385</v>
       </c>
-      <c r="G108" s="7"/>
+      <c r="G108" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="109" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
@@ -3833,10 +3998,12 @@
       <c r="E109" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F109" s="8">
+      <c r="F109" s="7">
         <v>45385</v>
       </c>
-      <c r="G109" s="7"/>
+      <c r="G109" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="110" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
@@ -3854,10 +4021,12 @@
       <c r="E110" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F110" s="8">
+      <c r="F110" s="7">
         <v>45385</v>
       </c>
-      <c r="G110" s="7"/>
+      <c r="G110" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="111" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
@@ -3875,10 +4044,12 @@
       <c r="E111" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F111" s="8">
+      <c r="F111" s="7">
         <v>45385</v>
       </c>
-      <c r="G111" s="7"/>
+      <c r="G111" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="112" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
@@ -3896,10 +4067,12 @@
       <c r="E112" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F112" s="8">
+      <c r="F112" s="7">
         <v>45385</v>
       </c>
-      <c r="G112" s="7"/>
+      <c r="G112" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="113" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="4">
@@ -3917,10 +4090,12 @@
       <c r="E113" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F113" s="8">
+      <c r="F113" s="7">
         <v>45385</v>
       </c>
-      <c r="G113" s="7"/>
+      <c r="G113" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="114" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="4">
@@ -3938,10 +4113,12 @@
       <c r="E114" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F114" s="8">
+      <c r="F114" s="7">
         <v>45385</v>
       </c>
-      <c r="G114" s="7"/>
+      <c r="G114" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="115" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
@@ -3959,10 +4136,12 @@
       <c r="E115" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F115" s="8">
+      <c r="F115" s="7">
         <v>45385</v>
       </c>
-      <c r="G115" s="7"/>
+      <c r="G115" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="116" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="4">
@@ -3980,10 +4159,12 @@
       <c r="E116" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F116" s="8">
+      <c r="F116" s="7">
         <v>45385</v>
       </c>
-      <c r="G116" s="7"/>
+      <c r="G116" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="117" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
@@ -4001,10 +4182,12 @@
       <c r="E117" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F117" s="8">
+      <c r="F117" s="7">
         <v>45385</v>
       </c>
-      <c r="G117" s="7"/>
+      <c r="G117" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="118" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="4">
@@ -4022,10 +4205,12 @@
       <c r="E118" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F118" s="8">
+      <c r="F118" s="7">
         <v>45385</v>
       </c>
-      <c r="G118" s="7"/>
+      <c r="G118" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="119" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
@@ -4043,10 +4228,12 @@
       <c r="E119" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F119" s="8">
+      <c r="F119" s="7">
         <v>45385</v>
       </c>
-      <c r="G119" s="7"/>
+      <c r="G119" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="120" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="4">
@@ -4064,10 +4251,12 @@
       <c r="E120" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F120" s="8">
+      <c r="F120" s="7">
         <v>45397</v>
       </c>
-      <c r="G120" s="7"/>
+      <c r="G120" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="121" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
@@ -4085,10 +4274,12 @@
       <c r="E121" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F121" s="8">
+      <c r="F121" s="7">
         <v>45397</v>
       </c>
-      <c r="G121" s="7"/>
+      <c r="G121" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="122" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="4">
@@ -4106,10 +4297,12 @@
       <c r="E122" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F122" s="8">
+      <c r="F122" s="7">
         <v>45397</v>
       </c>
-      <c r="G122" s="7"/>
+      <c r="G122" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="123" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
@@ -4127,10 +4320,12 @@
       <c r="E123" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F123" s="8">
+      <c r="F123" s="7">
         <v>45397</v>
       </c>
-      <c r="G123" s="7"/>
+      <c r="G123" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="124" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="4">
@@ -4148,10 +4343,12 @@
       <c r="E124" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F124" s="8">
+      <c r="F124" s="7">
         <v>45397</v>
       </c>
-      <c r="G124" s="7"/>
+      <c r="G124" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="125" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
@@ -4169,10 +4366,12 @@
       <c r="E125" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F125" s="8">
+      <c r="F125" s="7">
         <v>45397</v>
       </c>
-      <c r="G125" s="7"/>
+      <c r="G125" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="126" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="4">
@@ -4190,10 +4389,12 @@
       <c r="E126" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F126" s="8">
+      <c r="F126" s="7">
         <v>45397</v>
       </c>
-      <c r="G126" s="7"/>
+      <c r="G126" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="127" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="4">
@@ -4211,10 +4412,12 @@
       <c r="E127" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F127" s="8">
+      <c r="F127" s="7">
         <v>45397</v>
       </c>
-      <c r="G127" s="7"/>
+      <c r="G127" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="128" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="4">
@@ -4232,10 +4435,12 @@
       <c r="E128" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F128" s="8">
+      <c r="F128" s="7">
         <v>45397</v>
       </c>
-      <c r="G128" s="7"/>
+      <c r="G128" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="129" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="4">
@@ -4253,10 +4458,12 @@
       <c r="E129" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F129" s="8">
+      <c r="F129" s="7">
         <v>45397</v>
       </c>
-      <c r="G129" s="7"/>
+      <c r="G129" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="130" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="4">
@@ -4274,10 +4481,12 @@
       <c r="E130" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F130" s="8">
+      <c r="F130" s="7">
         <v>45397</v>
       </c>
-      <c r="G130" s="7"/>
+      <c r="G130" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="131" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="4">
@@ -4295,10 +4504,12 @@
       <c r="E131" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F131" s="8">
+      <c r="F131" s="7">
         <v>45397</v>
       </c>
-      <c r="G131" s="7"/>
+      <c r="G131" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="132" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="4">
@@ -4316,10 +4527,12 @@
       <c r="E132" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F132" s="8">
+      <c r="F132" s="7">
         <v>45397</v>
       </c>
-      <c r="G132" s="7"/>
+      <c r="G132" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="133" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="4">
@@ -4337,10 +4550,12 @@
       <c r="E133" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F133" s="8">
+      <c r="F133" s="7">
         <v>45397</v>
       </c>
-      <c r="G133" s="7"/>
+      <c r="G133" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="134" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="4">
@@ -4358,10 +4573,12 @@
       <c r="E134" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F134" s="8">
+      <c r="F134" s="7">
         <v>45397</v>
       </c>
-      <c r="G134" s="7"/>
+      <c r="G134" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="135" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
@@ -4379,10 +4596,12 @@
       <c r="E135" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F135" s="8">
+      <c r="F135" s="7">
         <v>45397</v>
       </c>
-      <c r="G135" s="7"/>
+      <c r="G135" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="136" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="4">
@@ -4400,10 +4619,12 @@
       <c r="E136" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F136" s="8">
+      <c r="F136" s="7">
         <v>45397</v>
       </c>
-      <c r="G136" s="7"/>
+      <c r="G136" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="137" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="4">
@@ -4421,10 +4642,12 @@
       <c r="E137" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F137" s="8">
+      <c r="F137" s="7">
         <v>45397</v>
       </c>
-      <c r="G137" s="7"/>
+      <c r="G137" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="138" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="4">
@@ -4442,10 +4665,12 @@
       <c r="E138" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F138" s="8">
+      <c r="F138" s="7">
         <v>45397</v>
       </c>
-      <c r="G138" s="7"/>
+      <c r="G138" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="139" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="4">
@@ -4463,10 +4688,12 @@
       <c r="E139" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F139" s="8">
+      <c r="F139" s="7">
         <v>45397</v>
       </c>
-      <c r="G139" s="7"/>
+      <c r="G139" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="140" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="4">
@@ -4484,10 +4711,12 @@
       <c r="E140" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F140" s="8">
+      <c r="F140" s="7">
         <v>45397</v>
       </c>
-      <c r="G140" s="7"/>
+      <c r="G140" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="141" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="4">
@@ -4505,10 +4734,12 @@
       <c r="E141" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F141" s="8">
+      <c r="F141" s="7">
         <v>45397</v>
       </c>
-      <c r="G141" s="7"/>
+      <c r="G141" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="142" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="4">
@@ -4526,10 +4757,12 @@
       <c r="E142" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F142" s="8">
+      <c r="F142" s="7">
         <v>45397</v>
       </c>
-      <c r="G142" s="7"/>
+      <c r="G142" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="143" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="4">
@@ -4547,10 +4780,12 @@
       <c r="E143" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F143" s="8">
+      <c r="F143" s="7">
         <v>45397</v>
       </c>
-      <c r="G143" s="7"/>
+      <c r="G143" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="144" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="4">
@@ -4568,10 +4803,12 @@
       <c r="E144" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F144" s="8">
+      <c r="F144" s="7">
         <v>45397</v>
       </c>
-      <c r="G144" s="7"/>
+      <c r="G144" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="145" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="4">
@@ -4589,10 +4826,12 @@
       <c r="E145" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F145" s="8">
+      <c r="F145" s="7">
         <v>45397</v>
       </c>
-      <c r="G145" s="7"/>
+      <c r="G145" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="146" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="4">
@@ -4610,10 +4849,12 @@
       <c r="E146" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F146" s="8">
+      <c r="F146" s="7">
         <v>45397</v>
       </c>
-      <c r="G146" s="7"/>
+      <c r="G146" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="147" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="4">
@@ -4631,10 +4872,12 @@
       <c r="E147" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F147" s="8">
+      <c r="F147" s="7">
         <v>45397</v>
       </c>
-      <c r="G147" s="7"/>
+      <c r="G147" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="148" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="4">
@@ -4652,10 +4895,12 @@
       <c r="E148" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F148" s="8">
+      <c r="F148" s="7">
         <v>45397</v>
       </c>
-      <c r="G148" s="7"/>
+      <c r="G148" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="149" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="4">
@@ -4673,10 +4918,12 @@
       <c r="E149" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F149" s="8">
+      <c r="F149" s="7">
         <v>45397</v>
       </c>
-      <c r="G149" s="7"/>
+      <c r="G149" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="150" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="4">
@@ -4694,10 +4941,12 @@
       <c r="E150" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F150" s="8">
+      <c r="F150" s="7">
         <v>45397</v>
       </c>
-      <c r="G150" s="7"/>
+      <c r="G150" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="151" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="4">
@@ -4715,10 +4964,12 @@
       <c r="E151" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F151" s="8">
+      <c r="F151" s="7">
         <v>45406</v>
       </c>
-      <c r="G151" s="7"/>
+      <c r="G151" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="152" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="4">
@@ -4736,10 +4987,12 @@
       <c r="E152" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F152" s="8">
+      <c r="F152" s="7">
         <v>45406</v>
       </c>
-      <c r="G152" s="7"/>
+      <c r="G152" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="153" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="4">
@@ -4757,10 +5010,12 @@
       <c r="E153" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F153" s="8">
+      <c r="F153" s="7">
         <v>45406</v>
       </c>
-      <c r="G153" s="7"/>
+      <c r="G153" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="154" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="4">
@@ -4778,10 +5033,12 @@
       <c r="E154" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F154" s="8">
+      <c r="F154" s="7">
         <v>45406</v>
       </c>
-      <c r="G154" s="7"/>
+      <c r="G154" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="155" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="4">
@@ -4799,10 +5056,12 @@
       <c r="E155" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F155" s="8">
+      <c r="F155" s="7">
         <v>45406</v>
       </c>
-      <c r="G155" s="7"/>
+      <c r="G155" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="156" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="4">
@@ -4820,10 +5079,12 @@
       <c r="E156" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F156" s="8">
+      <c r="F156" s="7">
         <v>45406</v>
       </c>
-      <c r="G156" s="7"/>
+      <c r="G156" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="157" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="4">
@@ -4841,10 +5102,12 @@
       <c r="E157" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F157" s="8">
+      <c r="F157" s="7">
         <v>45406</v>
       </c>
-      <c r="G157" s="7"/>
+      <c r="G157" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="158" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="4">
@@ -4862,10 +5125,12 @@
       <c r="E158" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F158" s="8">
+      <c r="F158" s="7">
         <v>45406</v>
       </c>
-      <c r="G158" s="7"/>
+      <c r="G158" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="159" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="4">
@@ -4883,10 +5148,12 @@
       <c r="E159" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F159" s="8">
+      <c r="F159" s="7">
         <v>45406</v>
       </c>
-      <c r="G159" s="7"/>
+      <c r="G159" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="160" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="4">
@@ -4904,10 +5171,12 @@
       <c r="E160" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F160" s="8">
+      <c r="F160" s="7">
         <v>45406</v>
       </c>
-      <c r="G160" s="7"/>
+      <c r="G160" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="161" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="4">
@@ -4925,10 +5194,12 @@
       <c r="E161" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F161" s="8">
+      <c r="F161" s="7">
         <v>45406</v>
       </c>
-      <c r="G161" s="7"/>
+      <c r="G161" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="162" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="4">
@@ -4946,10 +5217,12 @@
       <c r="E162" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F162" s="8">
+      <c r="F162" s="7">
         <v>45406</v>
       </c>
-      <c r="G162" s="7"/>
+      <c r="G162" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="163" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="4">
@@ -4967,10 +5240,12 @@
       <c r="E163" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F163" s="8">
+      <c r="F163" s="7">
         <v>45445</v>
       </c>
-      <c r="G163" s="7"/>
+      <c r="G163" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="164" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="4">
@@ -4988,10 +5263,12 @@
       <c r="E164" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F164" s="8">
+      <c r="F164" s="7">
         <v>45445</v>
       </c>
-      <c r="G164" s="7"/>
+      <c r="G164" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="165" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="4">
@@ -5009,10 +5286,12 @@
       <c r="E165" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F165" s="8">
+      <c r="F165" s="7">
         <v>45445</v>
       </c>
-      <c r="G165" s="7"/>
+      <c r="G165" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="166" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="4">
@@ -5030,10 +5309,12 @@
       <c r="E166" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F166" s="8">
+      <c r="F166" s="7">
         <v>45445</v>
       </c>
-      <c r="G166" s="7"/>
+      <c r="G166" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="167" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="4">
@@ -5051,10 +5332,12 @@
       <c r="E167" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F167" s="8">
+      <c r="F167" s="7">
         <v>45445</v>
       </c>
-      <c r="G167" s="7"/>
+      <c r="G167" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="168" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="4">
@@ -5072,10 +5355,12 @@
       <c r="E168" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F168" s="8">
+      <c r="F168" s="7">
         <v>45445</v>
       </c>
-      <c r="G168" s="7"/>
+      <c r="G168" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="169" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="4">
@@ -5093,10 +5378,12 @@
       <c r="E169" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F169" s="8">
+      <c r="F169" s="7">
         <v>45445</v>
       </c>
-      <c r="G169" s="7"/>
+      <c r="G169" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="170" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="4">
@@ -5114,10 +5401,12 @@
       <c r="E170" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F170" s="8">
+      <c r="F170" s="7">
         <v>45445</v>
       </c>
-      <c r="G170" s="7"/>
+      <c r="G170" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="171" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="4">
@@ -5135,10 +5424,12 @@
       <c r="E171" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F171" s="8">
+      <c r="F171" s="7">
         <v>45445</v>
       </c>
-      <c r="G171" s="7"/>
+      <c r="G171" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="172" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="4">
@@ -5156,10 +5447,12 @@
       <c r="E172" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F172" s="8">
+      <c r="F172" s="7">
         <v>45445</v>
       </c>
-      <c r="G172" s="7"/>
+      <c r="G172" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="173" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="4">
@@ -5177,10 +5470,12 @@
       <c r="E173" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F173" s="8">
+      <c r="F173" s="7">
         <v>45445</v>
       </c>
-      <c r="G173" s="7"/>
+      <c r="G173" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="174" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="4">
@@ -5198,10 +5493,12 @@
       <c r="E174" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F174" s="8">
+      <c r="F174" s="7">
         <v>45445</v>
       </c>
-      <c r="G174" s="7"/>
+      <c r="G174" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="175" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="4">
@@ -5219,10 +5516,12 @@
       <c r="E175" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F175" s="8">
+      <c r="F175" s="7">
         <v>45445</v>
       </c>
-      <c r="G175" s="7"/>
+      <c r="G175" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="176" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="4">
@@ -5240,10 +5539,12 @@
       <c r="E176" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F176" s="8">
+      <c r="F176" s="7">
         <v>45445</v>
       </c>
-      <c r="G176" s="7"/>
+      <c r="G176" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="177" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="4">
@@ -5261,10 +5562,12 @@
       <c r="E177" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F177" s="8">
+      <c r="F177" s="7">
         <v>45445</v>
       </c>
-      <c r="G177" s="7"/>
+      <c r="G177" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="178" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="4">
@@ -5282,10 +5585,12 @@
       <c r="E178" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F178" s="8">
+      <c r="F178" s="7">
         <v>45446</v>
       </c>
-      <c r="G178" s="7"/>
+      <c r="G178" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="179" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="4">
@@ -5303,10 +5608,12 @@
       <c r="E179" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F179" s="8">
+      <c r="F179" s="7">
         <v>45446</v>
       </c>
-      <c r="G179" s="7"/>
+      <c r="G179" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="180" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="4">
@@ -5324,10 +5631,12 @@
       <c r="E180" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F180" s="8">
+      <c r="F180" s="7">
         <v>45446</v>
       </c>
-      <c r="G180" s="7"/>
+      <c r="G180" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="181" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="4">
@@ -5345,10 +5654,12 @@
       <c r="E181" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F181" s="8">
+      <c r="F181" s="7">
         <v>45446</v>
       </c>
-      <c r="G181" s="7"/>
+      <c r="G181" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="182" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="4">
@@ -5366,10 +5677,12 @@
       <c r="E182" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F182" s="8">
+      <c r="F182" s="7">
         <v>45446</v>
       </c>
-      <c r="G182" s="7"/>
+      <c r="G182" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="183" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="4">
@@ -5387,10 +5700,12 @@
       <c r="E183" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F183" s="8">
+      <c r="F183" s="7">
         <v>45446</v>
       </c>
-      <c r="G183" s="7"/>
+      <c r="G183" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="184" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="4">
@@ -5408,10 +5723,12 @@
       <c r="E184" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F184" s="8">
+      <c r="F184" s="7">
         <v>45446</v>
       </c>
-      <c r="G184" s="7"/>
+      <c r="G184" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="185" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="4">
@@ -5429,10 +5746,12 @@
       <c r="E185" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F185" s="8">
+      <c r="F185" s="7">
         <v>45446</v>
       </c>
-      <c r="G185" s="7"/>
+      <c r="G185" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="186" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="4">
@@ -5450,10 +5769,12 @@
       <c r="E186" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F186" s="8">
+      <c r="F186" s="7">
         <v>45446</v>
       </c>
-      <c r="G186" s="7"/>
+      <c r="G186" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="187" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="4">
@@ -5471,10 +5792,12 @@
       <c r="E187" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F187" s="8">
+      <c r="F187" s="7">
         <v>45446</v>
       </c>
-      <c r="G187" s="7"/>
+      <c r="G187" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="188" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="4">
@@ -5492,10 +5815,12 @@
       <c r="E188" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F188" s="8">
+      <c r="F188" s="7">
         <v>45526</v>
       </c>
-      <c r="G188" s="7"/>
+      <c r="G188" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="189" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="4">
@@ -5513,10 +5838,12 @@
       <c r="E189" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F189" s="8">
+      <c r="F189" s="7">
         <v>45526</v>
       </c>
-      <c r="G189" s="7"/>
+      <c r="G189" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="190" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="4">
@@ -5534,10 +5861,12 @@
       <c r="E190" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F190" s="8">
+      <c r="F190" s="7">
         <v>45526</v>
       </c>
-      <c r="G190" s="7"/>
+      <c r="G190" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="191" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="4">
@@ -5555,10 +5884,12 @@
       <c r="E191" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F191" s="8">
+      <c r="F191" s="7">
         <v>45526</v>
       </c>
-      <c r="G191" s="7"/>
+      <c r="G191" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="192" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="4">
@@ -5576,10 +5907,12 @@
       <c r="E192" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F192" s="8">
+      <c r="F192" s="7">
         <v>45526</v>
       </c>
-      <c r="G192" s="7"/>
+      <c r="G192" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="193" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="4">
@@ -5597,10 +5930,12 @@
       <c r="E193" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F193" s="8">
+      <c r="F193" s="7">
         <v>45526</v>
       </c>
-      <c r="G193" s="7"/>
+      <c r="G193" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="194" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="4">
@@ -5618,10 +5953,12 @@
       <c r="E194" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F194" s="8">
+      <c r="F194" s="7">
         <v>45526</v>
       </c>
-      <c r="G194" s="7"/>
+      <c r="G194" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="195" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="4">
@@ -5639,10 +5976,12 @@
       <c r="E195" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F195" s="8">
+      <c r="F195" s="7">
         <v>45526</v>
       </c>
-      <c r="G195" s="7"/>
+      <c r="G195" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="196" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="4">
@@ -5660,10 +5999,12 @@
       <c r="E196" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F196" s="8">
+      <c r="F196" s="7">
         <v>45526</v>
       </c>
-      <c r="G196" s="7"/>
+      <c r="G196" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="197" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="4">
@@ -5681,10 +6022,12 @@
       <c r="E197" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F197" s="8">
+      <c r="F197" s="7">
         <v>45526</v>
       </c>
-      <c r="G197" s="7"/>
+      <c r="G197" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="198" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="4">
@@ -5702,10 +6045,12 @@
       <c r="E198" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F198" s="8">
+      <c r="F198" s="7">
         <v>45526</v>
       </c>
-      <c r="G198" s="7"/>
+      <c r="G198" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="199" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="4">
@@ -5723,10 +6068,12 @@
       <c r="E199" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F199" s="8">
+      <c r="F199" s="7">
         <v>45526</v>
       </c>
-      <c r="G199" s="7"/>
+      <c r="G199" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="200" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="4">
@@ -5744,10 +6091,12 @@
       <c r="E200" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F200" s="8">
+      <c r="F200" s="7">
         <v>45526</v>
       </c>
-      <c r="G200" s="7"/>
+      <c r="G200" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="201" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="4">
@@ -5765,10 +6114,12 @@
       <c r="E201" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F201" s="8">
+      <c r="F201" s="7">
         <v>45526</v>
       </c>
-      <c r="G201" s="7"/>
+      <c r="G201" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="202" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="4">
@@ -5786,10 +6137,12 @@
       <c r="E202" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F202" s="8">
+      <c r="F202" s="7">
         <v>45526</v>
       </c>
-      <c r="G202" s="7"/>
+      <c r="G202" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="203" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="4">
@@ -5807,10 +6160,12 @@
       <c r="E203" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F203" s="8">
+      <c r="F203" s="7">
         <v>45526</v>
       </c>
-      <c r="G203" s="7"/>
+      <c r="G203" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="204" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="4">
@@ -5828,10 +6183,12 @@
       <c r="E204" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F204" s="8">
+      <c r="F204" s="7">
         <v>45526</v>
       </c>
-      <c r="G204" s="7"/>
+      <c r="G204" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="205" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="4">
@@ -5849,10 +6206,12 @@
       <c r="E205" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F205" s="8">
+      <c r="F205" s="7">
         <v>45526</v>
       </c>
-      <c r="G205" s="7"/>
+      <c r="G205" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="206" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="4">
@@ -5870,10 +6229,12 @@
       <c r="E206" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F206" s="8">
+      <c r="F206" s="7">
         <v>45526</v>
       </c>
-      <c r="G206" s="7"/>
+      <c r="G206" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="207" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="4">
@@ -5891,10 +6252,12 @@
       <c r="E207" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F207" s="8">
+      <c r="F207" s="7">
         <v>45526</v>
       </c>
-      <c r="G207" s="7"/>
+      <c r="G207" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="208" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="4">
@@ -5912,10 +6275,12 @@
       <c r="E208" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F208" s="8">
+      <c r="F208" s="7">
         <v>45526</v>
       </c>
-      <c r="G208" s="7"/>
+      <c r="G208" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="209" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="4">
@@ -5933,10 +6298,12 @@
       <c r="E209" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F209" s="8">
+      <c r="F209" s="7">
         <v>45526</v>
       </c>
-      <c r="G209" s="7"/>
+      <c r="G209" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="210" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="4">
@@ -5954,10 +6321,12 @@
       <c r="E210" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F210" s="8">
+      <c r="F210" s="7">
         <v>45526</v>
       </c>
-      <c r="G210" s="7"/>
+      <c r="G210" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="211" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="4">
@@ -5975,10 +6344,12 @@
       <c r="E211" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F211" s="8">
+      <c r="F211" s="7">
         <v>45526</v>
       </c>
-      <c r="G211" s="7"/>
+      <c r="G211" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="212" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="4">
@@ -5996,10 +6367,12 @@
       <c r="E212" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F212" s="8">
+      <c r="F212" s="7">
         <v>45526</v>
       </c>
-      <c r="G212" s="7"/>
+      <c r="G212" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="213" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="4">
@@ -6017,10 +6390,12 @@
       <c r="E213" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F213" s="8">
+      <c r="F213" s="7">
         <v>45526</v>
       </c>
-      <c r="G213" s="7"/>
+      <c r="G213" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="214" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="4">
@@ -6038,10 +6413,12 @@
       <c r="E214" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F214" s="8">
+      <c r="F214" s="7">
         <v>45526</v>
       </c>
-      <c r="G214" s="7"/>
+      <c r="G214" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="215" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="4">
@@ -6059,10 +6436,12 @@
       <c r="E215" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F215" s="8">
+      <c r="F215" s="7">
         <v>45526</v>
       </c>
-      <c r="G215" s="7"/>
+      <c r="G215" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="216" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="4">
@@ -6080,10 +6459,12 @@
       <c r="E216" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F216" s="8">
+      <c r="F216" s="7">
         <v>45526</v>
       </c>
-      <c r="G216" s="7"/>
+      <c r="G216" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="217" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="4">
@@ -6101,10 +6482,12 @@
       <c r="E217" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F217" s="8">
+      <c r="F217" s="7">
         <v>45526</v>
       </c>
-      <c r="G217" s="7"/>
+      <c r="G217" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="218" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="4">
@@ -6122,10 +6505,12 @@
       <c r="E218" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F218" s="8">
+      <c r="F218" s="7">
         <v>45526</v>
       </c>
-      <c r="G218" s="7"/>
+      <c r="G218" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="219" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="4">
@@ -6143,10 +6528,12 @@
       <c r="E219" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F219" s="8">
+      <c r="F219" s="7">
         <v>45526</v>
       </c>
-      <c r="G219" s="7"/>
+      <c r="G219" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="220" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="4">
@@ -6164,10 +6551,12 @@
       <c r="E220" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F220" s="8">
+      <c r="F220" s="7">
         <v>45526</v>
       </c>
-      <c r="G220" s="7"/>
+      <c r="G220" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="221" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="4">
@@ -6185,10 +6574,12 @@
       <c r="E221" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F221" s="8">
+      <c r="F221" s="7">
         <v>45526</v>
       </c>
-      <c r="G221" s="7"/>
+      <c r="G221" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="222" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="4">
@@ -6206,10 +6597,12 @@
       <c r="E222" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F222" s="8">
+      <c r="F222" s="7">
         <v>45526</v>
       </c>
-      <c r="G222" s="7"/>
+      <c r="G222" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="223" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="4">
@@ -6227,10 +6620,12 @@
       <c r="E223" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F223" s="8">
+      <c r="F223" s="7">
         <v>45526</v>
       </c>
-      <c r="G223" s="7"/>
+      <c r="G223" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="224" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="4">
@@ -6248,10 +6643,12 @@
       <c r="E224" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F224" s="8">
+      <c r="F224" s="7">
         <v>45526</v>
       </c>
-      <c r="G224" s="7"/>
+      <c r="G224" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="225" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="4">
@@ -6269,10 +6666,12 @@
       <c r="E225" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F225" s="8">
+      <c r="F225" s="7">
         <v>45526</v>
       </c>
-      <c r="G225" s="7"/>
+      <c r="G225" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="226" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="4">
@@ -6290,10 +6689,12 @@
       <c r="E226" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F226" s="8">
+      <c r="F226" s="7">
         <v>45526</v>
       </c>
-      <c r="G226" s="7"/>
+      <c r="G226" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="227" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="4">
@@ -6311,10 +6712,12 @@
       <c r="E227" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F227" s="8">
+      <c r="F227" s="7">
         <v>45526</v>
       </c>
-      <c r="G227" s="7"/>
+      <c r="G227" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="228" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="4">
@@ -6332,10 +6735,12 @@
       <c r="E228" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F228" s="8">
+      <c r="F228" s="7">
         <v>45526</v>
       </c>
-      <c r="G228" s="7"/>
+      <c r="G228" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="229" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="4">
@@ -6353,10 +6758,12 @@
       <c r="E229" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F229" s="8">
+      <c r="F229" s="7">
         <v>45526</v>
       </c>
-      <c r="G229" s="7"/>
+      <c r="G229" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="230" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="4">
@@ -6374,10 +6781,12 @@
       <c r="E230" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F230" s="8">
+      <c r="F230" s="7">
         <v>45526</v>
       </c>
-      <c r="G230" s="7"/>
+      <c r="G230" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="231" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="4">
@@ -6395,10 +6804,12 @@
       <c r="E231" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F231" s="8">
+      <c r="F231" s="7">
         <v>45526</v>
       </c>
-      <c r="G231" s="7"/>
+      <c r="G231" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="232" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="4">
@@ -6416,10 +6827,12 @@
       <c r="E232" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F232" s="8">
+      <c r="F232" s="7">
         <v>45526</v>
       </c>
-      <c r="G232" s="7"/>
+      <c r="G232" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="233" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="4">
@@ -6437,10 +6850,12 @@
       <c r="E233" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F233" s="8">
+      <c r="F233" s="7">
         <v>45526</v>
       </c>
-      <c r="G233" s="7"/>
+      <c r="G233" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="234" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="4">
@@ -6458,10 +6873,12 @@
       <c r="E234" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F234" s="8">
+      <c r="F234" s="7">
         <v>45526</v>
       </c>
-      <c r="G234" s="7"/>
+      <c r="G234" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="235" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="4">
@@ -6479,10 +6896,12 @@
       <c r="E235" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F235" s="8">
+      <c r="F235" s="7">
         <v>45544</v>
       </c>
-      <c r="G235" s="7"/>
+      <c r="G235" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="236" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="4">
@@ -6500,10 +6919,12 @@
       <c r="E236" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F236" s="8">
+      <c r="F236" s="7">
         <v>45544</v>
       </c>
-      <c r="G236" s="7"/>
+      <c r="G236" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="237" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="4">
@@ -6521,10 +6942,12 @@
       <c r="E237" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F237" s="8">
+      <c r="F237" s="7">
         <v>45544</v>
       </c>
-      <c r="G237" s="7"/>
+      <c r="G237" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="238" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="4">
@@ -6542,10 +6965,12 @@
       <c r="E238" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F238" s="8">
+      <c r="F238" s="7">
         <v>45544</v>
       </c>
-      <c r="G238" s="7"/>
+      <c r="G238" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="239" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="4">
@@ -6563,10 +6988,12 @@
       <c r="E239" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F239" s="8">
+      <c r="F239" s="7">
         <v>45544</v>
       </c>
-      <c r="G239" s="7"/>
+      <c r="G239" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="240" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="4">
@@ -6584,10 +7011,12 @@
       <c r="E240" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F240" s="8">
+      <c r="F240" s="7">
         <v>45544</v>
       </c>
-      <c r="G240" s="7"/>
+      <c r="G240" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="241" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="4">
@@ -6605,10 +7034,12 @@
       <c r="E241" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F241" s="8">
+      <c r="F241" s="7">
         <v>45544</v>
       </c>
-      <c r="G241" s="7"/>
+      <c r="G241" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="242" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="4">
@@ -6626,10 +7057,12 @@
       <c r="E242" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F242" s="8">
+      <c r="F242" s="7">
         <v>45544</v>
       </c>
-      <c r="G242" s="7"/>
+      <c r="G242" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="243" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="4">
@@ -6647,10 +7080,12 @@
       <c r="E243" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F243" s="8">
+      <c r="F243" s="7">
         <v>45544</v>
       </c>
-      <c r="G243" s="7"/>
+      <c r="G243" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="244" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="4">
@@ -6668,10 +7103,12 @@
       <c r="E244" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F244" s="8">
+      <c r="F244" s="7">
         <v>45544</v>
       </c>
-      <c r="G244" s="7"/>
+      <c r="G244" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="245" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="4">
@@ -6689,10 +7126,12 @@
       <c r="E245" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F245" s="8">
+      <c r="F245" s="7">
         <v>45544</v>
       </c>
-      <c r="G245" s="7"/>
+      <c r="G245" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="246" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="4">
@@ -6710,10 +7149,12 @@
       <c r="E246" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F246" s="8">
+      <c r="F246" s="7">
         <v>45544</v>
       </c>
-      <c r="G246" s="7"/>
+      <c r="G246" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="247" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="4">
@@ -6731,10 +7172,12 @@
       <c r="E247" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F247" s="8">
+      <c r="F247" s="7">
         <v>45544</v>
       </c>
-      <c r="G247" s="7"/>
+      <c r="G247" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="248" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="4">
@@ -6752,10 +7195,12 @@
       <c r="E248" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F248" s="8">
+      <c r="F248" s="7">
         <v>45544</v>
       </c>
-      <c r="G248" s="7"/>
+      <c r="G248" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="249" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="4">
@@ -6773,10 +7218,12 @@
       <c r="E249" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F249" s="8">
+      <c r="F249" s="7">
         <v>45544</v>
       </c>
-      <c r="G249" s="7"/>
+      <c r="G249" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="250" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="4">
@@ -6794,10 +7241,12 @@
       <c r="E250" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F250" s="8">
+      <c r="F250" s="7">
         <v>45544</v>
       </c>
-      <c r="G250" s="7"/>
+      <c r="G250" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="251" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="4">
@@ -6815,10 +7264,12 @@
       <c r="E251" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F251" s="8">
+      <c r="F251" s="7">
         <v>45544</v>
       </c>
-      <c r="G251" s="7"/>
+      <c r="G251" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="252" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="4">
@@ -6836,10 +7287,12 @@
       <c r="E252" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F252" s="8">
+      <c r="F252" s="7">
         <v>45544</v>
       </c>
-      <c r="G252" s="7"/>
+      <c r="G252" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="253" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="4">
@@ -6857,10 +7310,12 @@
       <c r="E253" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F253" s="8">
+      <c r="F253" s="7">
         <v>45544</v>
       </c>
-      <c r="G253" s="7"/>
+      <c r="G253" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="254" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="4">
@@ -6878,10 +7333,12 @@
       <c r="E254" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F254" s="8">
+      <c r="F254" s="7">
         <v>45544</v>
       </c>
-      <c r="G254" s="7"/>
+      <c r="G254" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="255" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="4">
@@ -6899,10 +7356,12 @@
       <c r="E255" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F255" s="8">
+      <c r="F255" s="7">
         <v>45544</v>
       </c>
-      <c r="G255" s="7"/>
+      <c r="G255" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="256" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="4">
@@ -6920,10 +7379,12 @@
       <c r="E256" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F256" s="8">
+      <c r="F256" s="7">
         <v>45544</v>
       </c>
-      <c r="G256" s="7"/>
+      <c r="G256" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="257" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="4">
@@ -6941,10 +7402,12 @@
       <c r="E257" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F257" s="8">
+      <c r="F257" s="7">
         <v>45544</v>
       </c>
-      <c r="G257" s="7"/>
+      <c r="G257" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="258" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="4">
@@ -6962,10 +7425,12 @@
       <c r="E258" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F258" s="8">
+      <c r="F258" s="7">
         <v>45544</v>
       </c>
-      <c r="G258" s="7"/>
+      <c r="G258" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="259" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="4">
@@ -6983,10 +7448,12 @@
       <c r="E259" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F259" s="8">
+      <c r="F259" s="7">
         <v>45544</v>
       </c>
-      <c r="G259" s="7"/>
+      <c r="G259" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="260" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="4">
@@ -7004,10 +7471,12 @@
       <c r="E260" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F260" s="8">
+      <c r="F260" s="7">
         <v>45544</v>
       </c>
-      <c r="G260" s="7"/>
+      <c r="G260" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="261" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="4">
@@ -7025,10 +7494,12 @@
       <c r="E261" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F261" s="8">
+      <c r="F261" s="7">
         <v>45544</v>
       </c>
-      <c r="G261" s="7"/>
+      <c r="G261" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="262" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="4">
@@ -7046,10 +7517,12 @@
       <c r="E262" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F262" s="8">
+      <c r="F262" s="7">
         <v>45544</v>
       </c>
-      <c r="G262" s="7"/>
+      <c r="G262" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="263" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="4">
@@ -7067,10 +7540,12 @@
       <c r="E263" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F263" s="8">
+      <c r="F263" s="7">
         <v>45544</v>
       </c>
-      <c r="G263" s="7"/>
+      <c r="G263" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="264" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="4">
@@ -7088,10 +7563,12 @@
       <c r="E264" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F264" s="8">
+      <c r="F264" s="7">
         <v>45544</v>
       </c>
-      <c r="G264" s="7"/>
+      <c r="G264" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="265" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="4">
@@ -7109,10 +7586,12 @@
       <c r="E265" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F265" s="8">
+      <c r="F265" s="7">
         <v>45544</v>
       </c>
-      <c r="G265" s="7"/>
+      <c r="G265" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="266" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="4">
@@ -7130,10 +7609,12 @@
       <c r="E266" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F266" s="8">
+      <c r="F266" s="7">
         <v>45544</v>
       </c>
-      <c r="G266" s="7"/>
+      <c r="G266" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="267" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="4">
@@ -7151,10 +7632,12 @@
       <c r="E267" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F267" s="8">
+      <c r="F267" s="7">
         <v>45544</v>
       </c>
-      <c r="G267" s="7"/>
+      <c r="G267" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="268" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="4">
@@ -7172,10 +7655,12 @@
       <c r="E268" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F268" s="8">
+      <c r="F268" s="7">
         <v>45544</v>
       </c>
-      <c r="G268" s="7"/>
+      <c r="G268" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="269" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="4">
@@ -7193,10 +7678,12 @@
       <c r="E269" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F269" s="8">
+      <c r="F269" s="7">
         <v>45544</v>
       </c>
-      <c r="G269" s="7"/>
+      <c r="G269" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="270" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="4">
@@ -7214,10 +7701,12 @@
       <c r="E270" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F270" s="8">
+      <c r="F270" s="7">
         <v>45544</v>
       </c>
-      <c r="G270" s="7"/>
+      <c r="G270" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="271" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="4">
@@ -7235,10 +7724,12 @@
       <c r="E271" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F271" s="8">
+      <c r="F271" s="7">
         <v>45581</v>
       </c>
-      <c r="G271" s="7"/>
+      <c r="G271" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="272" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="4">
@@ -7256,10 +7747,12 @@
       <c r="E272" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F272" s="8">
+      <c r="F272" s="7">
         <v>45581</v>
       </c>
-      <c r="G272" s="7"/>
+      <c r="G272" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="273" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="4">
@@ -7277,10 +7770,12 @@
       <c r="E273" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F273" s="8">
+      <c r="F273" s="7">
         <v>45581</v>
       </c>
-      <c r="G273" s="7"/>
+      <c r="G273" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="274" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="4">
@@ -7298,10 +7793,12 @@
       <c r="E274" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F274" s="8">
+      <c r="F274" s="7">
         <v>45581</v>
       </c>
-      <c r="G274" s="7"/>
+      <c r="G274" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="275" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="4">
@@ -7319,10 +7816,12 @@
       <c r="E275" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F275" s="8">
+      <c r="F275" s="7">
         <v>45581</v>
       </c>
-      <c r="G275" s="7"/>
+      <c r="G275" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="276" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="4">
@@ -7340,10 +7839,12 @@
       <c r="E276" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F276" s="8">
+      <c r="F276" s="7">
         <v>45581</v>
       </c>
-      <c r="G276" s="7"/>
+      <c r="G276" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="277" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="4">
@@ -7361,10 +7862,12 @@
       <c r="E277" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F277" s="8">
+      <c r="F277" s="7">
         <v>45581</v>
       </c>
-      <c r="G277" s="7"/>
+      <c r="G277" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="278" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="4">
@@ -7382,10 +7885,12 @@
       <c r="E278" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F278" s="8">
+      <c r="F278" s="7">
         <v>45581</v>
       </c>
-      <c r="G278" s="7"/>
+      <c r="G278" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="279" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="4">
@@ -7403,10 +7908,12 @@
       <c r="E279" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F279" s="8">
+      <c r="F279" s="7">
         <v>45581</v>
       </c>
-      <c r="G279" s="7"/>
+      <c r="G279" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="280" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="4">
@@ -7424,10 +7931,12 @@
       <c r="E280" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F280" s="8">
+      <c r="F280" s="7">
         <v>45581</v>
       </c>
-      <c r="G280" s="7"/>
+      <c r="G280" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="281" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="4">
@@ -7445,10 +7954,12 @@
       <c r="E281" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F281" s="8">
+      <c r="F281" s="7">
         <v>45581</v>
       </c>
-      <c r="G281" s="7"/>
+      <c r="G281" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="282" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="4">
@@ -7466,10 +7977,12 @@
       <c r="E282" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F282" s="8">
+      <c r="F282" s="7">
         <v>45581</v>
       </c>
-      <c r="G282" s="7"/>
+      <c r="G282" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="283" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="4">
@@ -7487,10 +8000,12 @@
       <c r="E283" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F283" s="8">
+      <c r="F283" s="7">
         <v>45581</v>
       </c>
-      <c r="G283" s="7"/>
+      <c r="G283" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="284" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="4">
@@ -7508,10 +8023,12 @@
       <c r="E284" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F284" s="8">
+      <c r="F284" s="7">
         <v>45581</v>
       </c>
-      <c r="G284" s="7"/>
+      <c r="G284" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="285" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="4">
@@ -7529,10 +8046,12 @@
       <c r="E285" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F285" s="8">
+      <c r="F285" s="7">
         <v>45609</v>
       </c>
-      <c r="G285" s="7"/>
+      <c r="G285" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="286" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="4">
@@ -7550,10 +8069,12 @@
       <c r="E286" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F286" s="8">
+      <c r="F286" s="7">
         <v>45609</v>
       </c>
-      <c r="G286" s="7"/>
+      <c r="G286" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="287" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="4">
@@ -7571,10 +8092,12 @@
       <c r="E287" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F287" s="8">
+      <c r="F287" s="7">
         <v>45609</v>
       </c>
-      <c r="G287" s="7"/>
+      <c r="G287" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="288" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="4">
@@ -7592,10 +8115,12 @@
       <c r="E288" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F288" s="8">
+      <c r="F288" s="7">
         <v>45609</v>
       </c>
-      <c r="G288" s="7"/>
+      <c r="G288" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="289" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="4">
@@ -7613,10 +8138,12 @@
       <c r="E289" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F289" s="8">
+      <c r="F289" s="7">
         <v>45609</v>
       </c>
-      <c r="G289" s="7"/>
+      <c r="G289" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="290" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="4">
@@ -7634,10 +8161,12 @@
       <c r="E290" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F290" s="8">
+      <c r="F290" s="7">
         <v>45609</v>
       </c>
-      <c r="G290" s="7"/>
+      <c r="G290" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="291" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="4">
@@ -7655,10 +8184,12 @@
       <c r="E291" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F291" s="8">
+      <c r="F291" s="7">
         <v>45609</v>
       </c>
-      <c r="G291" s="7"/>
+      <c r="G291" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="292" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="4">
@@ -7676,10 +8207,12 @@
       <c r="E292" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F292" s="8">
+      <c r="F292" s="7">
         <v>45631</v>
       </c>
-      <c r="G292" s="7"/>
+      <c r="G292" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="293" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="4">
@@ -7697,10 +8230,12 @@
       <c r="E293" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F293" s="8">
+      <c r="F293" s="7">
         <v>45631</v>
       </c>
-      <c r="G293" s="7"/>
+      <c r="G293" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="294" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="4">
@@ -7718,10 +8253,12 @@
       <c r="E294" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F294" s="8">
+      <c r="F294" s="7">
         <v>45631</v>
       </c>
-      <c r="G294" s="7"/>
+      <c r="G294" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="295" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="4">
@@ -7739,10 +8276,12 @@
       <c r="E295" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F295" s="8">
+      <c r="F295" s="7">
         <v>45631</v>
       </c>
-      <c r="G295" s="7"/>
+      <c r="G295" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="296" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="4">
@@ -7760,10 +8299,12 @@
       <c r="E296" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F296" s="8">
+      <c r="F296" s="7">
         <v>45631</v>
       </c>
-      <c r="G296" s="7"/>
+      <c r="G296" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="297" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="4">
@@ -7781,10 +8322,12 @@
       <c r="E297" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F297" s="8">
+      <c r="F297" s="7">
         <v>46037</v>
       </c>
-      <c r="G297" s="7"/>
+      <c r="G297" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="298" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="4">
@@ -7802,10 +8345,12 @@
       <c r="E298" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F298" s="8">
+      <c r="F298" s="7">
         <v>46037</v>
       </c>
-      <c r="G298" s="7"/>
+      <c r="G298" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="299" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="4">
@@ -7823,10 +8368,12 @@
       <c r="E299" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F299" s="8">
+      <c r="F299" s="7">
         <v>46037</v>
       </c>
-      <c r="G299" s="7"/>
+      <c r="G299" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="300" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="4">
@@ -7844,10 +8391,12 @@
       <c r="E300" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F300" s="8">
+      <c r="F300" s="7">
         <v>46037</v>
       </c>
-      <c r="G300" s="7"/>
+      <c r="G300" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="301" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="4">
@@ -7865,10 +8414,12 @@
       <c r="E301" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F301" s="8">
+      <c r="F301" s="7">
         <v>46037</v>
       </c>
-      <c r="G301" s="7"/>
+      <c r="G301" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="302" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="4">
@@ -7886,10 +8437,12 @@
       <c r="E302" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F302" s="8">
+      <c r="F302" s="7">
         <v>46037</v>
       </c>
-      <c r="G302" s="7"/>
+      <c r="G302" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="303" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="4">
@@ -7907,10 +8460,12 @@
       <c r="E303" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F303" s="8">
+      <c r="F303" s="7">
         <v>46037</v>
       </c>
-      <c r="G303" s="7"/>
+      <c r="G303" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="304" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="4">
@@ -7928,10 +8483,12 @@
       <c r="E304" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F304" s="8">
+      <c r="F304" s="7">
         <v>46037</v>
       </c>
-      <c r="G304" s="7"/>
+      <c r="G304" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="305" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="4">
@@ -7949,10 +8506,12 @@
       <c r="E305" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F305" s="8">
+      <c r="F305" s="7">
         <v>46037</v>
       </c>
-      <c r="G305" s="7"/>
+      <c r="G305" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="306" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="4">
@@ -7970,10 +8529,12 @@
       <c r="E306" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F306" s="8">
+      <c r="F306" s="7">
         <v>46037</v>
       </c>
-      <c r="G306" s="7"/>
+      <c r="G306" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="307" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="4">
@@ -7991,10 +8552,12 @@
       <c r="E307" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F307" s="8">
+      <c r="F307" s="7">
         <v>46037</v>
       </c>
-      <c r="G307" s="7"/>
+      <c r="G307" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="308" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="4">
@@ -8012,10 +8575,12 @@
       <c r="E308" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F308" s="8">
+      <c r="F308" s="7">
         <v>46037</v>
       </c>
-      <c r="G308" s="7"/>
+      <c r="G308" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="309" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="4">
@@ -8033,10 +8598,12 @@
       <c r="E309" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F309" s="8">
+      <c r="F309" s="7">
         <v>46037</v>
       </c>
-      <c r="G309" s="7"/>
+      <c r="G309" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="310" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="4">
@@ -8054,10 +8621,12 @@
       <c r="E310" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F310" s="8">
+      <c r="F310" s="7">
         <v>46117</v>
       </c>
-      <c r="G310" s="7"/>
+      <c r="G310" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="311" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="4">
@@ -8075,10 +8644,12 @@
       <c r="E311" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F311" s="8">
+      <c r="F311" s="7">
         <v>46117</v>
       </c>
-      <c r="G311" s="7"/>
+      <c r="G311" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="312" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="4">
@@ -8096,10 +8667,12 @@
       <c r="E312" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F312" s="8">
+      <c r="F312" s="7">
         <v>46117</v>
       </c>
-      <c r="G312" s="7"/>
+      <c r="G312" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="313" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="4">
@@ -8117,10 +8690,12 @@
       <c r="E313" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F313" s="8">
+      <c r="F313" s="7">
         <v>46117</v>
       </c>
-      <c r="G313" s="7"/>
+      <c r="G313" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="314" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="4">
@@ -8138,10 +8713,12 @@
       <c r="E314" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F314" s="8">
+      <c r="F314" s="7">
         <v>46117</v>
       </c>
-      <c r="G314" s="7"/>
+      <c r="G314" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="315" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="4">
@@ -8159,10 +8736,12 @@
       <c r="E315" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F315" s="8">
+      <c r="F315" s="7">
         <v>46117</v>
       </c>
-      <c r="G315" s="7"/>
+      <c r="G315" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="316" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="4">
@@ -8180,10 +8759,12 @@
       <c r="E316" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F316" s="8">
+      <c r="F316" s="7">
         <v>46117</v>
       </c>
-      <c r="G316" s="7"/>
+      <c r="G316" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="317" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="4">
@@ -8201,10 +8782,12 @@
       <c r="E317" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F317" s="8">
+      <c r="F317" s="7">
         <v>46117</v>
       </c>
-      <c r="G317" s="7"/>
+      <c r="G317" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="318" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="4">
@@ -8222,10 +8805,12 @@
       <c r="E318" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F318" s="8">
+      <c r="F318" s="7">
         <v>46117</v>
       </c>
-      <c r="G318" s="7"/>
+      <c r="G318" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="319" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="4">
@@ -8243,10 +8828,12 @@
       <c r="E319" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F319" s="8">
+      <c r="F319" s="7">
         <v>46117</v>
       </c>
-      <c r="G319" s="7"/>
+      <c r="G319" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="320" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="4">
@@ -8264,10 +8851,12 @@
       <c r="E320" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F320" s="8">
+      <c r="F320" s="7">
         <v>46117</v>
       </c>
-      <c r="G320" s="7"/>
+      <c r="G320" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="321" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="4">
@@ -8285,10 +8874,12 @@
       <c r="E321" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F321" s="8">
+      <c r="F321" s="7">
         <v>46117</v>
       </c>
-      <c r="G321" s="7"/>
+      <c r="G321" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="322" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="4">
@@ -8306,10 +8897,12 @@
       <c r="E322" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F322" s="8">
+      <c r="F322" s="7">
         <v>46117</v>
       </c>
-      <c r="G322" s="7"/>
+      <c r="G322" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="323" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="4">
@@ -8327,10 +8920,12 @@
       <c r="E323" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F323" s="8">
+      <c r="F323" s="7">
         <v>46117</v>
       </c>
-      <c r="G323" s="7"/>
+      <c r="G323" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="324" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="4">
@@ -8348,10 +8943,12 @@
       <c r="E324" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F324" s="8">
+      <c r="F324" s="7">
         <v>46117</v>
       </c>
-      <c r="G324" s="7"/>
+      <c r="G324" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="325" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="4">
@@ -8369,10 +8966,12 @@
       <c r="E325" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F325" s="8">
+      <c r="F325" s="7">
         <v>46117</v>
       </c>
-      <c r="G325" s="7"/>
+      <c r="G325" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="326" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="4">
@@ -8390,10 +8989,12 @@
       <c r="E326" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F326" s="8">
+      <c r="F326" s="7">
         <v>46117</v>
       </c>
-      <c r="G326" s="7"/>
+      <c r="G326" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="327" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="4">
@@ -8411,10 +9012,12 @@
       <c r="E327" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F327" s="8">
+      <c r="F327" s="7">
         <v>46117</v>
       </c>
-      <c r="G327" s="7"/>
+      <c r="G327" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="328" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="4">
@@ -8432,10 +9035,12 @@
       <c r="E328" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F328" s="8">
+      <c r="F328" s="7">
         <v>46117</v>
       </c>
-      <c r="G328" s="7"/>
+      <c r="G328" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="329" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="4">
@@ -8453,10 +9058,12 @@
       <c r="E329" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F329" s="8">
+      <c r="F329" s="7">
         <v>46117</v>
       </c>
-      <c r="G329" s="7"/>
+      <c r="G329" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="330" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="4">
@@ -8474,10 +9081,12 @@
       <c r="E330" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F330" s="8">
+      <c r="F330" s="7">
         <v>46117</v>
       </c>
-      <c r="G330" s="7"/>
+      <c r="G330" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="331" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="4">
@@ -8495,10 +9104,12 @@
       <c r="E331" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F331" s="8">
+      <c r="F331" s="7">
         <v>46117</v>
       </c>
-      <c r="G331" s="7"/>
+      <c r="G331" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="332" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="4">
@@ -8516,10 +9127,12 @@
       <c r="E332" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F332" s="8">
+      <c r="F332" s="7">
         <v>46117</v>
       </c>
-      <c r="G332" s="7"/>
+      <c r="G332" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="333" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="4">
@@ -8537,10 +9150,12 @@
       <c r="E333" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F333" s="8">
+      <c r="F333" s="7">
         <v>46117</v>
       </c>
-      <c r="G333" s="7"/>
+      <c r="G333" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="334" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="4">
@@ -8558,10 +9173,12 @@
       <c r="E334" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F334" s="8">
+      <c r="F334" s="7">
         <v>46117</v>
       </c>
-      <c r="G334" s="7"/>
+      <c r="G334" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="335" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="4">
@@ -8579,10 +9196,12 @@
       <c r="E335" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F335" s="8">
+      <c r="F335" s="7">
         <v>46198</v>
       </c>
-      <c r="G335" s="7"/>
+      <c r="G335" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="336" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="4">
@@ -8600,10 +9219,12 @@
       <c r="E336" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F336" s="8">
+      <c r="F336" s="7">
         <v>46198</v>
       </c>
-      <c r="G336" s="7"/>
+      <c r="G336" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="337" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="4">
@@ -8621,10 +9242,12 @@
       <c r="E337" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F337" s="8">
+      <c r="F337" s="7">
         <v>46198</v>
       </c>
-      <c r="G337" s="7"/>
+      <c r="G337" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="338" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="4">
@@ -8642,10 +9265,12 @@
       <c r="E338" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F338" s="8">
+      <c r="F338" s="7">
         <v>46198</v>
       </c>
-      <c r="G338" s="7"/>
+      <c r="G338" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="339" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="4">
@@ -8663,10 +9288,12 @@
       <c r="E339" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F339" s="8">
+      <c r="F339" s="7">
         <v>46198</v>
       </c>
-      <c r="G339" s="7"/>
+      <c r="G339" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="340" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="4">
@@ -8684,10 +9311,12 @@
       <c r="E340" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F340" s="8">
+      <c r="F340" s="7">
         <v>46198</v>
       </c>
-      <c r="G340" s="7"/>
+      <c r="G340" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="341" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="4">
@@ -8705,10 +9334,12 @@
       <c r="E341" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F341" s="8">
+      <c r="F341" s="7">
         <v>46198</v>
       </c>
-      <c r="G341" s="7"/>
+      <c r="G341" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="342" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="4">
@@ -8726,10 +9357,12 @@
       <c r="E342" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F342" s="8">
+      <c r="F342" s="7">
         <v>46198</v>
       </c>
-      <c r="G342" s="7"/>
+      <c r="G342" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="343" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="4">
@@ -8747,10 +9380,12 @@
       <c r="E343" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F343" s="8">
+      <c r="F343" s="7">
         <v>46198</v>
       </c>
-      <c r="G343" s="7"/>
+      <c r="G343" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="344" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="4">
@@ -8768,10 +9403,12 @@
       <c r="E344" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F344" s="8">
+      <c r="F344" s="7">
         <v>46198</v>
       </c>
-      <c r="G344" s="7"/>
+      <c r="G344" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="345" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="4">
@@ -8789,10 +9426,12 @@
       <c r="E345" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F345" s="8">
+      <c r="F345" s="7">
         <v>46198</v>
       </c>
-      <c r="G345" s="7"/>
+      <c r="G345" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8803,7 +9442,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8812,7 +9451,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
